--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487837_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487837_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9307</v>
+        <v>4.5608</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6811</v>
+        <v>4.2524</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2496</v>
+        <v>0.3083</v>
       </c>
       <c r="G2" t="n">
         <v>2.5525</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1442</v>
+        <v>-0.5141</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3849</v>
+        <v>-0.0438</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5291</v>
+        <v>-0.4703</v>
       </c>
       <c r="V2" t="n">
         <v>1.2737</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.54</v>
+        <v>4.4724</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9491</v>
+        <v>2.7348</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5908</v>
+        <v>1.7376</v>
       </c>
       <c r="G3" t="n">
         <v>2.5478</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0078</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0033</v>
+        <v>-0.2176</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7393</v>
+        <v>4.3132</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9218</v>
+        <v>3.6719</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8175</v>
+        <v>0.6413</v>
       </c>
       <c r="G4" t="n">
         <v>2.2415</v>
@@ -766,13 +766,13 @@
         <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5834</v>
+        <v>-1.0094</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0439</v>
+        <v>-0.2938</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5395</v>
+        <v>-0.7156</v>
       </c>
       <c r="V4" t="n">
         <v>0.5838</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3581</v>
+        <v>0.2632</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7057</v>
+        <v>0.7385</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0638</v>
+        <v>-0.4754</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8702</v>
+        <v>-0.065</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1641</v>
+        <v>0.276</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9598</v>
+        <v>1.7518</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0774</v>
+        <v>0.341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176</v>
+        <v>1.4108</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0897</v>
+        <v>-1.8168</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3713</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>-1.1348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1474</v>
+        <v>-1.0693</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1272</v>
+        <v>-0.3295</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2746</v>
+        <v>-0.7398</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2338</v>
+        <v>0.1041</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7385</v>
+        <v>-0.8129</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5047</v>
+        <v>0.917</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.065</v>
+        <v>-0.8702</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.341</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.276</v>
+        <v>-0.1641</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7518</v>
+        <v>-0.9598</v>
       </c>
       <c r="K6" t="n">
-        <v>0.341</v>
+        <v>-1.0774</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4108</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8168</v>
+        <v>0.0897</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.3713</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1348</v>
+        <v>-0.2817</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0986</v>
+        <v>-0.4014</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3295</v>
+        <v>0.02</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7691</v>
+        <v>-0.4214</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2496</v>
+        <v>-0.3186</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1911</v>
+        <v>-0.0839</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0585</v>
+        <v>-0.2347</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2813</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1546</v>
+        <v>-0.2236</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1716</v>
+        <v>-0.0045</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1029</v>
+        <v>-0.8593</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0683</v>
+        <v>0.146</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0346</v>
+        <v>-1.0052</v>
       </c>
       <c r="G8" t="n">
         <v>1.129</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.67</v>
+        <v>-0.4264</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0828</v>
+        <v>-0.0535</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9376</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3553</v>
+        <v>-2.4738</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6311</v>
+        <v>-2.4222</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9864</v>
+        <v>-0.0515</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8335</v>
+        <v>-0.875</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0319</v>
+        <v>2.8635</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1984</v>
+        <v>-3.7384</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3236</v>
+        <v>-0.785</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7055</v>
+        <v>2.6392</v>
       </c>
       <c r="L9" t="n">
-        <v>0.618</v>
+        <v>-3.4241</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4901</v>
+        <v>-0.09</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6737</v>
+        <v>0.2243</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8164</v>
+        <v>-0.3143</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4568</v>
+        <v>2.9137</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1025</v>
+        <v>-1.1368</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4907</v>
+        <v>-0.5967</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3882</v>
+        <v>-0.5401</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6264</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.0614</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.565</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3516</v>
+        <v>-3.5341</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0652</v>
+        <v>-0.5476</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2864</v>
+        <v>-2.9864</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.875</v>
+        <v>1.8335</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8635</v>
+        <v>2.0319</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7384</v>
+        <v>-0.1984</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.785</v>
+        <v>3.3236</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6392</v>
+        <v>2.7055</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.4241</v>
+        <v>0.618</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09</v>
+        <v>-1.4901</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2243</v>
+        <v>-0.6737</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3143</v>
+        <v>-0.8164</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8731</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9137</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0146</v>
+        <v>-0.0762</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2396</v>
+        <v>0.312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.775</v>
+        <v>-0.3882</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.3351</v>
+        <v>-3.6264</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.0614</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3351</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6726</v>
+        <v>-5.4583</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9782</v>
+        <v>-2.7638</v>
       </c>
       <c r="F11" t="n">
         <v>-2.6945</v>
@@ -1312,10 +1312,10 @@
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5467</v>
+        <v>-0.3324</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2857</v>
@@ -1345,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.069900000000001</v>
+        <v>1.0696</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9131</v>
+        <v>4.913200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8434</v>
+        <v>-3.8435</v>
       </c>
       <c r="G12" t="n">
         <v>5.919400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7359</v>
+        <v>5.735900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1837000000000004</v>
+        <v>0.1837000000000009</v>
       </c>
       <c r="J12" t="n">
         <v>14.6567</v>
       </c>
       <c r="K12" t="n">
-        <v>8.4518</v>
+        <v>8.451799999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>6.204700000000001</v>
+        <v>6.2047</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.737200000000001</v>
+        <v>-8.7372</v>
       </c>
       <c r="N12" t="n">
         <v>-2.7163</v>
@@ -1390,16 +1390,16 @@
         <v>16.6494</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.264799999999999</v>
+        <v>-5.265000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7879</v>
+        <v>-1.7881</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4769</v>
+        <v>-3.4768</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.706599999999999</v>
+        <v>-2.7066</v>
       </c>
       <c r="W12" t="n">
         <v>5.5722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5265</v>
+        <v>4.2678</v>
       </c>
       <c r="E13" t="n">
-        <v>6.221</v>
+        <v>6.7568</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6944</v>
+        <v>-2.4889</v>
       </c>
       <c r="G13" t="n">
         <v>2.921</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7483</v>
+        <v>-0.007</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.64</v>
+        <v>-0.1043</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1083</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.9376</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0417</v>
+        <v>2.798</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4174</v>
+        <v>2.2031</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6243</v>
+        <v>0.5949</v>
       </c>
       <c r="G14" t="n">
         <v>2.0803</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4619</v>
+        <v>0.2182</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2042</v>
+        <v>0.1749</v>
       </c>
       <c r="V14" t="n">
         <v>0.7076</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5985</v>
+        <v>1.8128</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4415</v>
+        <v>1.6558</v>
       </c>
       <c r="F15" t="n">
         <v>0.157</v>
@@ -1624,10 +1624,10 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1429</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3262</v>
+        <v>-0.1119</v>
       </c>
       <c r="U15" t="n">
         <v>0.1833</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0554</v>
+        <v>0.8562</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8089</v>
+        <v>1.8012</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8643</v>
+        <v>-0.945</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9647</v>
+        <v>-2.5874</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3858</v>
+        <v>-1.3048</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5788</v>
+        <v>-1.2826</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0766</v>
+        <v>-0.7339</v>
       </c>
       <c r="K16" t="n">
-        <v>0.341</v>
+        <v>-0.6228</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7356</v>
+        <v>-0.1111</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0412</v>
+        <v>-1.8535</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7268</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3144</v>
+        <v>-1.1716</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1392</v>
+        <v>0.403</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4378</v>
+        <v>0.4082</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7014</v>
+        <v>-0.0052</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5838</v>
+        <v>2.3351</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0969</v>
+        <v>0.3922</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7991</v>
+        <v>0.8447</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7022</v>
+        <v>-0.4525</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4819</v>
+        <v>-0.3439</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0257</v>
+        <v>-1.0126</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5437</v>
+        <v>0.6686</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2736</v>
+        <v>1.7505</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.352</v>
+        <v>0.0532</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>1.6973</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2083</v>
+        <v>-2.0944</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6737</v>
+        <v>-1.0657</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4654</v>
+        <v>-1.0287</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.5498</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3882</v>
+        <v>0.3429</v>
       </c>
       <c r="U17" t="n">
-        <v>0.308</v>
+        <v>0.2069</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5213</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1442</v>
+        <v>-0.5065</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5648</v>
+        <v>-2.1206</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.709</v>
+        <v>1.6141</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4681</v>
+        <v>-1.4819</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3368</v>
+        <v>-2.0257</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.805</v>
+        <v>0.5437</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2549</v>
+        <v>-1.2736</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3535</v>
+        <v>-1.352</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9013</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.723</v>
+        <v>-0.2083</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0167</v>
+        <v>-0.6737</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7063</v>
+        <v>0.4654</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.9137</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3705</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5914</v>
+        <v>0.2866</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4505</v>
+        <v>0.0667</v>
       </c>
       <c r="U18" t="n">
-        <v>0.141</v>
+        <v>0.2199</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3538</v>
+        <v>1.5213</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5838</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.528</v>
+        <v>-0.9141</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.2731</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1505</v>
+        <v>-1.1872</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5874</v>
+        <v>-0.9647</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3048</v>
+        <v>-0.3858</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2826</v>
+        <v>-0.5788</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7339</v>
+        <v>1.0766</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6228</v>
+        <v>0.341</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1111</v>
+        <v>0.7356</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8535</v>
+        <v>-2.0412</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.7268</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1716</v>
+        <v>-1.3144</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.2893</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.8731</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.2081</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.0812</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.9812</v>
+        <v>1.2805</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7705</v>
+        <v>0.9021</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2107</v>
+        <v>0.3785</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1675</v>
+        <v>-0.8137</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3351</v>
+        <v>0.5838</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>L. SORENSEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7278</v>
+        <v>-0.9643</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.334</v>
+        <v>-1.2453</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3938</v>
+        <v>0.281</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3439</v>
+        <v>-1.806</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0126</v>
+        <v>-2.2069</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6686</v>
+        <v>0.4009</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7505</v>
+        <v>-1.312</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0532</v>
+        <v>-1.3904</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6973</v>
+        <v>0.0784</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0944</v>
+        <v>-0.494</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0657</v>
+        <v>-0.8165</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0287</v>
+        <v>0.3225</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5702</v>
+        <v>0.2174</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8358</v>
+        <v>0.0667</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2656</v>
+        <v>0.1507</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SORENSEN</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.819</v>
+        <v>-2.1508</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9238</v>
+        <v>-0.4711</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1049</v>
+        <v>-1.6796</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.806</v>
+        <v>-0.4681</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2069</v>
+        <v>0.3368</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4009</v>
+        <v>-0.805</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.312</v>
+        <v>2.2549</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3904</v>
+        <v>1.3535</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0784</v>
+        <v>0.9013</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.494</v>
+        <v>-2.723</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8165</v>
+        <v>-1.0167</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3225</v>
+        <v>-1.7063</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6244</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.3705</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3627</v>
+        <v>1.5848</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3882</v>
+        <v>1.4145</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0254</v>
+        <v>0.1703</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8651</v>
+        <v>-6.6611</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1756</v>
+        <v>-5.8542</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6895</v>
+        <v>-0.8069</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1994</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.456</v>
+        <v>0.6601</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1272</v>
+        <v>0.4487</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3289</v>
+        <v>0.2114</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0697</v>
+        <v>-1.0698</v>
       </c>
       <c r="E23" t="n">
-        <v>3.843599999999999</v>
+        <v>3.843500000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-4.9131</v>
@@ -2218,7 +2218,7 @@
         <v>-5.7357</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1837000000000004</v>
+        <v>-0.1837000000000009</v>
       </c>
       <c r="J23" t="n">
         <v>8.737300000000001</v>
@@ -2236,7 +2236,7 @@
         <v>-8.4519</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.2047</v>
+        <v>-6.204699999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-3.1218</v>
@@ -2248,19 +2248,19 @@
         <v>13.5277</v>
       </c>
       <c r="S23" t="n">
-        <v>5.264700000000001</v>
+        <v>5.264799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4771</v>
+        <v>3.477</v>
       </c>
       <c r="U23" t="n">
-        <v>1.788</v>
+        <v>1.7879</v>
       </c>
       <c r="V23" t="n">
         <v>2.7065</v>
       </c>
       <c r="W23" t="n">
-        <v>8.279</v>
+        <v>8.279000000000002</v>
       </c>
       <c r="X23" t="n">
         <v>-5.5724</v>
